--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_09AM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_09AM.xlsx
@@ -1273,16 +1273,16 @@
         <v>547</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>49.3</v>
+        <v>47</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>841</v>
+        <v>802</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>10.2</v>
+        <v>12.4</v>
       </c>
       <c r="I4" s="30" t="n">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="J4" s="30" t="n">
         <v>8.5</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O4" s="32" t="n">
@@ -1441,16 +1441,16 @@
         <v>1300</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>29.3</v>
+        <v>26.2</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>626</v>
+        <v>560</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>5.8</v>
+        <v>8.9</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="J5" s="30" t="n">
         <v>4</v>
@@ -1609,16 +1609,16 @@
         <v>3829</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>26.4</v>
+        <v>25</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>1554</v>
+        <v>1474</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="I6" s="30" t="n">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>7.4</v>
@@ -2329,16 +2329,16 @@
         <v>85</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>35.6</v>
+        <v>27.6</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>11.4</v>
+        <v>19.3</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>37.7</v>
@@ -3041,16 +3041,16 @@
         <v>3491</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>16.2</v>
+        <v>11.6</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>1064</v>
+        <v>760</v>
       </c>
       <c r="H14" s="30" t="n">
-        <v>11.1</v>
+        <v>15.8</v>
       </c>
       <c r="I14" s="30" t="n">
-        <v>731</v>
+        <v>1034</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>19.4</v>
@@ -3219,16 +3219,16 @@
         <v>3348</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>18.4</v>
+        <v>14.8</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>1041</v>
+        <v>839</v>
       </c>
       <c r="H15" s="30" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="I15" s="30" t="n">
-        <v>364</v>
+        <v>566</v>
       </c>
       <c r="J15" s="30" t="n">
         <v>16.2</v>
@@ -3397,16 +3397,16 @@
         <v>224</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>39.4</v>
+        <v>20.2</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>286</v>
+        <v>147</v>
       </c>
       <c r="H16" s="30" t="n">
-        <v>16.3</v>
+        <v>35.5</v>
       </c>
       <c r="I16" s="30" t="n">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="J16" s="30" t="n">
         <v>13.5</v>
@@ -3575,16 +3575,16 @@
         <v>748</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>33.2</v>
+        <v>14.9</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>717</v>
+        <v>321</v>
       </c>
       <c r="H17" s="30" t="n">
-        <v>20</v>
+        <v>38.3</v>
       </c>
       <c r="I17" s="30" t="n">
-        <v>432</v>
+        <v>828</v>
       </c>
       <c r="J17" s="30" t="n">
         <v>12.2</v>
@@ -3753,16 +3753,16 @@
         <v>4496</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>6199</v>
+        <v>5875</v>
       </c>
       <c r="H18" s="30" t="n">
-        <v>6.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I18" s="30" t="n">
-        <v>734</v>
+        <v>1058</v>
       </c>
       <c r="J18" s="30" t="n">
         <v>5.5</v>
@@ -3931,16 +3931,16 @@
         <v>2733</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>30.3</v>
+        <v>26.7</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>1547</v>
+        <v>1365</v>
       </c>
       <c r="H19" s="30" t="n">
-        <v>8.699999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>443</v>
+        <v>625</v>
       </c>
       <c r="J19" s="30" t="n">
         <v>7.5</v>
@@ -4123,16 +4123,16 @@
         <v>2522</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>37</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>1724</v>
+        <v>1093</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>3.8</v>
+        <v>17.4</v>
       </c>
       <c r="I20" s="30" t="n">
-        <v>178</v>
+        <v>809</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>5.1</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="N20" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O20" s="32" t="n">
@@ -4301,16 +4301,16 @@
         <v>2567</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>30.3</v>
+        <v>25.8</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>1529</v>
+        <v>1300</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>5.7</v>
+        <v>10.3</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>290</v>
+        <v>519</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>13.1</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="N21" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O21" s="32" t="n">
@@ -4479,16 +4479,16 @@
         <v>14103</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>4058</v>
+        <v>3987</v>
       </c>
       <c r="H22" s="30" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I22" s="30" t="n">
-        <v>414</v>
+        <v>485</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>8.4</v>
@@ -4657,16 +4657,16 @@
         <v>5435</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>24.7</v>
+        <v>16.7</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>2519</v>
+        <v>1703</v>
       </c>
       <c r="H23" s="30" t="n">
-        <v>7.2</v>
+        <v>15.2</v>
       </c>
       <c r="I23" s="30" t="n">
-        <v>738</v>
+        <v>1554</v>
       </c>
       <c r="J23" s="30" t="n">
         <v>14.8</v>
@@ -4835,16 +4835,16 @@
         <v>2558</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>43.2</v>
+        <v>25.3</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>3962</v>
+        <v>2325</v>
       </c>
       <c r="H24" s="30" t="n">
-        <v>7.5</v>
+        <v>25.3</v>
       </c>
       <c r="I24" s="30" t="n">
-        <v>688</v>
+        <v>2325</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>21.5</v>
@@ -5013,16 +5013,16 @@
         <v>687</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>39.6</v>
+        <v>27.4</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>718</v>
+        <v>496</v>
       </c>
       <c r="H25" s="30" t="n">
-        <v>6.1</v>
+        <v>18.3</v>
       </c>
       <c r="I25" s="30" t="n">
-        <v>110</v>
+        <v>332</v>
       </c>
       <c r="J25" s="30" t="n">
         <v>16.4</v>
@@ -5191,16 +5191,16 @@
         <v>1793</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>35.4</v>
+        <v>26.1</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>1553</v>
+        <v>1144</v>
       </c>
       <c r="H26" s="30" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="I26" s="30" t="n">
-        <v>610</v>
+        <v>1019</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>9.800000000000001</v>
@@ -5369,16 +5369,16 @@
         <v>183</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>25.2</v>
+        <v>24.1</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H27" s="30" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="I27" s="30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>5.5</v>
@@ -5547,16 +5547,16 @@
         <v>237</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>24.3</v>
+        <v>15.4</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="H28" s="30" t="n">
-        <v>14.6</v>
+        <v>23.5</v>
       </c>
       <c r="I28" s="30" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="J28" s="30" t="n">
         <v>8</v>
@@ -5725,16 +5725,16 @@
         <v>117</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H29" s="30" t="n">
-        <v>9.9</v>
+        <v>11.6</v>
       </c>
       <c r="I29" s="30" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J29" s="30" t="n">
         <v>7.2</v>
@@ -5903,16 +5903,16 @@
         <v>493</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>41.7</v>
+        <v>30.6</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>537</v>
+        <v>394</v>
       </c>
       <c r="H30" s="30" t="n">
-        <v>12.7</v>
+        <v>23.8</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>163</v>
+        <v>306</v>
       </c>
       <c r="J30" s="30" t="n">
         <v>7.4</v>
@@ -6081,16 +6081,16 @@
         <v>896</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>23.6</v>
+        <v>18.9</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="H31" s="30" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="I31" s="30" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="J31" s="30" t="n">
         <v>3.5</v>
@@ -6437,16 +6437,16 @@
         <v>585</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>30.6</v>
+        <v>29.9</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="H33" s="30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J33" s="30" t="n">
         <v>14.1</v>
@@ -6615,16 +6615,16 @@
         <v>546</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>28.5</v>
+        <v>19.2</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>862</v>
+        <v>581</v>
       </c>
       <c r="H34" s="30" t="n">
-        <v>40.4</v>
+        <v>49.7</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>1222</v>
+        <v>1503</v>
       </c>
       <c r="J34" s="30" t="n">
         <v>13</v>
@@ -6793,16 +6793,16 @@
         <v>6361</v>
       </c>
       <c r="F35" s="30" t="n">
-        <v>24.1</v>
+        <v>21.5</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>2502</v>
+        <v>2224</v>
       </c>
       <c r="H35" s="30" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>281</v>
+        <v>559</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>11.8</v>
@@ -6971,16 +6971,16 @@
         <v>1522</v>
       </c>
       <c r="F36" s="30" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H36" s="30" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J36" s="30" t="n">
         <v>6.9</v>
@@ -7327,16 +7327,16 @@
         <v>14103</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>20.6</v>
+        <v>17</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>4461</v>
+        <v>3674</v>
       </c>
       <c r="H38" s="30" t="n">
-        <v>7.2</v>
+        <v>10.8</v>
       </c>
       <c r="I38" s="30" t="n">
-        <v>1547</v>
+        <v>2333</v>
       </c>
       <c r="J38" s="30" t="n">
         <v>7</v>
@@ -7505,16 +7505,16 @@
         <v>1595</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>1029</v>
+        <v>910</v>
       </c>
       <c r="H39" s="30" t="n">
-        <v>30.5</v>
+        <v>33</v>
       </c>
       <c r="I39" s="30" t="n">
-        <v>1422</v>
+        <v>1541</v>
       </c>
       <c r="J39" s="30" t="n">
         <v>13.4</v>
@@ -7683,16 +7683,16 @@
         <v>9241</v>
       </c>
       <c r="F40" s="30" t="n">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>2055</v>
+        <v>1712</v>
       </c>
       <c r="H40" s="30" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="I40" s="30" t="n">
-        <v>374</v>
+        <v>717</v>
       </c>
       <c r="J40" s="30" t="n">
         <v>7.1</v>
@@ -7861,16 +7861,16 @@
         <v>4589</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>25.6</v>
+        <v>24.2</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>1733</v>
+        <v>1639</v>
       </c>
       <c r="H41" s="30" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="I41" s="30" t="n">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="J41" s="30" t="n">
         <v>5</v>
@@ -8039,16 +8039,16 @@
         <v>573</v>
       </c>
       <c r="F42" s="30" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H42" s="30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I42" s="30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J42" s="30" t="n">
         <v>3.3</v>
@@ -8217,16 +8217,16 @@
         <v>8418</v>
       </c>
       <c r="F43" s="30" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>2815</v>
+        <v>2752</v>
       </c>
       <c r="H43" s="30" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="J43" s="30" t="n">
         <v>15.5</v>
@@ -8395,16 +8395,16 @@
         <v>531</v>
       </c>
       <c r="F44" s="30" t="n">
-        <v>47.2</v>
+        <v>42.1</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>654</v>
+        <v>584</v>
       </c>
       <c r="H44" s="30" t="n">
-        <v>5.1</v>
+        <v>10.2</v>
       </c>
       <c r="I44" s="30" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="J44" s="30" t="n">
         <v>9.5</v>
@@ -8573,16 +8573,16 @@
         <v>30</v>
       </c>
       <c r="F45" s="30" t="n">
-        <v>37.3</v>
+        <v>30</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H45" s="30" t="n">
-        <v>13.9</v>
+        <v>21.2</v>
       </c>
       <c r="I45" s="30" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J45" s="30" t="n">
         <v>12.5</v>
@@ -8949,16 +8949,16 @@
         <v>1575</v>
       </c>
       <c r="F47" s="30" t="n">
-        <v>28.1</v>
+        <v>23.6</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>1237</v>
+        <v>1041</v>
       </c>
       <c r="H47" s="30" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>293</v>
+        <v>490</v>
       </c>
       <c r="J47" s="30" t="n">
         <v>29.5</v>
@@ -9295,16 +9295,16 @@
         <v>3024</v>
       </c>
       <c r="F49" s="30" t="n">
-        <v>19.1</v>
+        <v>18.6</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>832</v>
+        <v>809</v>
       </c>
       <c r="H49" s="30" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="I49" s="30" t="n">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="J49" s="30" t="n">
         <v>5.9</v>
@@ -9473,16 +9473,16 @@
         <v>5647</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>29.2</v>
+        <v>24.5</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>3301</v>
+        <v>2771</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="I50" s="30" t="n">
-        <v>430</v>
+        <v>961</v>
       </c>
       <c r="J50" s="30" t="n">
         <v>17</v>
@@ -9829,16 +9829,16 @@
         <v>3400</v>
       </c>
       <c r="F52" s="30" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="G52" s="30" t="n">
-        <v>2205</v>
+        <v>2198</v>
       </c>
       <c r="H52" s="30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I52" s="30" t="n">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="J52" s="30" t="n">
         <v>13.8</v>
@@ -10007,16 +10007,16 @@
         <v>174</v>
       </c>
       <c r="F53" s="30" t="n">
-        <v>41.3</v>
+        <v>36.7</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="H53" s="30" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="I53" s="30" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="J53" s="30" t="n">
         <v>32.7</v>
@@ -10205,16 +10205,16 @@
         <v>1006</v>
       </c>
       <c r="F54" s="30" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="G54" s="30" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H54" s="30" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I54" s="30" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J54" s="30" t="n">
         <v>10.3</v>
@@ -10561,16 +10561,16 @@
         <v>290</v>
       </c>
       <c r="F56" s="30" t="n">
-        <v>31.3</v>
+        <v>26.7</v>
       </c>
       <c r="G56" s="30" t="n">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="H56" s="30" t="n">
-        <v>10.8</v>
+        <v>15.4</v>
       </c>
       <c r="I56" s="30" t="n">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="J56" s="30" t="n">
         <v>27.2</v>
@@ -10739,16 +10739,16 @@
         <v>2349</v>
       </c>
       <c r="F57" s="30" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>774</v>
+        <v>752</v>
       </c>
       <c r="H57" s="30" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I57" s="30" t="n">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J57" s="30" t="n">
         <v>11.8</v>
@@ -10917,16 +10917,16 @@
         <v>3969</v>
       </c>
       <c r="F58" s="30" t="n">
-        <v>28.8</v>
+        <v>24.9</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>2024</v>
+        <v>1751</v>
       </c>
       <c r="H58" s="30" t="n">
-        <v>6.8</v>
+        <v>10.7</v>
       </c>
       <c r="I58" s="30" t="n">
-        <v>480</v>
+        <v>753</v>
       </c>
       <c r="J58" s="30" t="n">
         <v>7.8</v>
@@ -11095,16 +11095,16 @@
         <v>2787</v>
       </c>
       <c r="F59" s="30" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="G59" s="30" t="n">
-        <v>1701</v>
+        <v>1661</v>
       </c>
       <c r="H59" s="30" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="I59" s="30" t="n">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="J59" s="30" t="n">
         <v>8.300000000000001</v>
@@ -11469,16 +11469,16 @@
         <v>974</v>
       </c>
       <c r="F61" s="30" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="G61" s="30" t="n">
-        <v>1241</v>
+        <v>1219</v>
       </c>
       <c r="H61" s="30" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="I61" s="30" t="n">
-        <v>1575</v>
+        <v>1596</v>
       </c>
       <c r="J61" s="30" t="n">
         <v>7.5</v>
@@ -12397,16 +12397,16 @@
         <v>20435</v>
       </c>
       <c r="F66" s="30" t="n">
-        <v>33.4</v>
+        <v>8</v>
       </c>
       <c r="G66" s="30" t="n">
-        <v>11723</v>
+        <v>2804</v>
       </c>
       <c r="H66" s="30" t="n">
-        <v>2.6</v>
+        <v>28</v>
       </c>
       <c r="I66" s="30" t="n">
-        <v>911</v>
+        <v>9830</v>
       </c>
       <c r="J66" s="30" t="n">
         <v>5.8</v>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="N66" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O66" s="32" t="n">
